--- a/authorization_forms/028_statement_of_financial_needs_authorization_form--authorization_forms.xlsx
+++ b/authorization_forms/028_statement_of_financial_needs_authorization_form--authorization_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1154,8 +1154,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1183,12 +1183,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'financial_needs',_'text':_'financial_needs'}</t>
+          <t>financial_needs</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Financial Needs', 'text': 'Financial Needs'}</t>
+          <t>Financial Needs</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'resources_and_authorization',_'text':_'resources_and_authorization'}</t>
+          <t>resources_and_authorization</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Resources and Authorization', 'text': 'Resources and Authorization'}</t>
+          <t>Resources and Authorization</t>
         </is>
       </c>
     </row>
@@ -1217,12 +1217,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'text':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Other', 'text': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'financial_aid',_'text':_'financial_aid'}</t>
+          <t>financial_aid</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Financial Aid', 'text': 'Financial Aid'}</t>
+          <t>Financial Aid</t>
         </is>
       </c>
     </row>
@@ -1251,12 +1251,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'resources',_'text':_'resources'}</t>
+          <t>resources</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Resources', 'text': 'Resources'}</t>
+          <t>Resources</t>
         </is>
       </c>
     </row>
@@ -1268,12 +1268,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'text':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Other', 'text': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1285,12 +1285,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'employed',_'text':_'employed'}</t>
+          <t>employed</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Employed', 'text': 'Employed'}</t>
+          <t>Employed</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'unemployed',_'text':_'unemployed'}</t>
+          <t>unemployed</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Unemployed', 'text': 'Unemployed'}</t>
+          <t>Unemployed</t>
         </is>
       </c>
     </row>
@@ -1319,12 +1319,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'student',_'text':_'student'}</t>
+          <t>student</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Student', 'text': 'Student'}</t>
+          <t>Student</t>
         </is>
       </c>
     </row>
@@ -1336,12 +1336,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'disabled',_'text':_'disabled'}</t>
+          <t>disabled</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Disabled', 'text': 'Disabled'}</t>
+          <t>Disabled</t>
         </is>
       </c>
     </row>
@@ -1353,12 +1353,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'authorized',_'text':_'authorized'}</t>
+          <t>authorized</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Authorized', 'text': 'Authorized'}</t>
+          <t>Authorized</t>
         </is>
       </c>
     </row>
@@ -1370,12 +1370,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'not_authorized',_'text':_'not_authorized'}</t>
+          <t>not_authorized</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Not Authorized', 'text': 'Not Authorized'}</t>
+          <t>Not Authorized</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'approved',_'text':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Approved', 'text': 'Approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1404,12 +1404,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'not_approved',_'text':_'not_approved'}</t>
+          <t>not_approved</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Not Approved', 'text': 'Not Approved'}</t>
+          <t>Not Approved</t>
         </is>
       </c>
     </row>
@@ -1421,12 +1421,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'pending',_'text':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Pending', 'text': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
